--- a/reto_dos/prueba_de_escritorio.xlsx
+++ b/reto_dos/prueba_de_escritorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Desktop\Entregable_momento_uno\reto_dos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29C803B5-1FD6-43CC-9BDC-63A2B2744C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F2CB35-206B-43AF-B5C3-7FC960E112D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9377FF27-FE9F-4C22-91DE-08A361FC0583}"/>
   </bookViews>
